--- a/datasets/20261021_recontrataciones_nuevo leon.xlsx
+++ b/datasets/20261021_recontrataciones_nuevo leon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabriela.bernal\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\INE\Documents\reductor_dias\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B735DBE-CA2E-43B4-BDFA-936F4D542E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FCC9790-5481-4E87-86CE-41E01E76C989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D3C7E6B5-2A0E-4AF2-BE80-0C96F41EC4B0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D3C7E6B5-2A0E-4AF2-BE80-0C96F41EC4B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Avance" sheetId="8" r:id="rId1"/>
@@ -161,9 +161,6 @@
     <t>Cabe señalar que muchas de las personas que participaron en 2024, con evaluación aprobatoria y sin actas administrativas, también prestaron sus servicios en 2025, por lo que se contabilizaron en este último año para evitar duplicidades.</t>
   </si>
   <si>
-    <t>Genera Escobedo</t>
-  </si>
-  <si>
     <t>03</t>
   </si>
   <si>
@@ -188,6 +185,9 @@
       </rPr>
       <t>en Nuevo León</t>
     </r>
+  </si>
+  <si>
+    <t>General Escobedo</t>
   </si>
 </sst>
 </file>
@@ -533,78 +533,78 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1027,50 +1027,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:22" s="2" customFormat="1" ht="25" x14ac:dyDescent="0.3">
-      <c r="C2" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="27"/>
+      <c r="C2" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
     </row>
     <row r="3" spans="2:22" s="2" customFormat="1" ht="20" x14ac:dyDescent="0.3">
-      <c r="C3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
+      <c r="C3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="17"/>
     </row>
     <row r="4" spans="2:22" s="2" customFormat="1" ht="20" x14ac:dyDescent="0.3">
       <c r="C4" s="1"/>
@@ -1094,92 +1094,92 @@
       <c r="U4" s="1"/>
     </row>
     <row r="5" spans="2:22" s="2" customFormat="1" ht="27" x14ac:dyDescent="0.5">
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="30"/>
+      <c r="S5" s="30"/>
       <c r="T5" s="5"/>
       <c r="U5" s="5"/>
     </row>
     <row r="6" spans="2:22" s="2" customFormat="1" ht="25" x14ac:dyDescent="0.5">
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="31"/>
       <c r="T6" s="6"/>
       <c r="U6" s="6"/>
     </row>
     <row r="7" spans="2:22" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.3">
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="2:22" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.3">
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="17">
+      <c r="C8" s="26"/>
+      <c r="D8" s="32">
         <v>46315</v>
       </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="19"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="34"/>
     </row>
     <row r="9" spans="2:22" s="2" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="26"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="26"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="37"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="37"/>
+      <c r="R9" s="37"/>
+      <c r="S9" s="37"/>
+      <c r="T9" s="37"/>
+      <c r="U9" s="37"/>
     </row>
     <row r="10" spans="2:22" s="2" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="15" t="s">
@@ -1188,30 +1188,30 @@
       <c r="C10" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="31" t="s">
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32"/>
-      <c r="O10" s="33" t="s">
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="30"/>
-      <c r="R10" s="30"/>
-      <c r="S10" s="34"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="28"/>
       <c r="T10" s="15" t="s">
         <v>11</v>
       </c>
@@ -1222,20 +1222,20 @@
     <row r="11" spans="2:22" s="2" customFormat="1" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="20" t="s">
+      <c r="D11" s="29"/>
+      <c r="E11" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="H11" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="22" t="s">
         <v>17</v>
       </c>
       <c r="J11" s="24" t="s">
@@ -1253,19 +1253,19 @@
       <c r="N11" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="O11" s="20" t="s">
+      <c r="O11" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="P11" s="20" t="s">
+      <c r="P11" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="Q11" s="20" t="s">
+      <c r="Q11" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="R11" s="20" t="s">
+      <c r="R11" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="S11" s="22" t="s">
+      <c r="S11" s="35" t="s">
         <v>17</v>
       </c>
       <c r="T11" s="15"/>
@@ -1278,26 +1278,26 @@
       <c r="C12" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="35"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
       <c r="J12" s="25"/>
       <c r="K12" s="25"/>
       <c r="L12" s="25"/>
       <c r="M12" s="25"/>
       <c r="N12" s="25"/>
-      <c r="O12" s="21"/>
-      <c r="P12" s="21"/>
-      <c r="Q12" s="21"/>
-      <c r="R12" s="21"/>
-      <c r="S12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
+      <c r="S12" s="36"/>
       <c r="T12" s="15"/>
       <c r="U12" s="15"/>
     </row>
-    <row r="13" spans="2:22" s="36" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:22" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="8">
         <v>19</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>117</v>
       </c>
       <c r="U13" s="12"/>
-      <c r="V13" s="37"/>
+      <c r="V13" s="14"/>
     </row>
     <row r="14" spans="2:22" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.3">
       <c r="B14" s="7">
@@ -1425,10 +1425,10 @@
         <v>19</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E15" s="11">
         <v>51</v>
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>36</v>
@@ -1606,7 +1606,7 @@
         <v>19</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>36</v>
@@ -2030,7 +2030,7 @@
         <v>13</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E25" s="11">
         <v>46</v>
@@ -2720,6 +2720,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="B9:U9"/>
+    <mergeCell ref="T10:T12"/>
     <mergeCell ref="U10:U12"/>
     <mergeCell ref="C2:U2"/>
     <mergeCell ref="C3:U3"/>
@@ -2736,21 +2751,6 @@
     <mergeCell ref="Q11:Q12"/>
     <mergeCell ref="R11:R12"/>
     <mergeCell ref="C5:S5"/>
-    <mergeCell ref="C6:S6"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="B9:U9"/>
-    <mergeCell ref="T10:T12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="78" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
